--- a/test/assets/template.xlsx
+++ b/test/assets/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Frontend\NPM\exceljs-xlsx-template\test\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35B5DBA-3D1E-405B-9040-0D8D6DF69DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393B2B6B-CE6E-4BA0-9047-D306350AF9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{657964AE-D3D3-40C6-8F0A-0275CA7E1F85}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
   <si>
     <t xml:space="preserve">中华人民共和国海关出口货物报关单  </t>
   </si>
@@ -351,6 +351,13 @@
       <t>{{phone}}</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{@@items.quantity}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国</t>
   </si>
 </sst>
 </file>
@@ -2922,12 +2929,16 @@
       </c>
       <c r="D17" s="71"/>
       <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
+      <c r="F17" s="25" t="s">
+        <v>76</v>
+      </c>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
       <c r="I17" s="27"/>
       <c r="J17" s="28"/>
-      <c r="K17" s="23"/>
+      <c r="K17" s="23" t="s">
+        <v>77</v>
+      </c>
       <c r="L17" s="72"/>
       <c r="M17" s="73"/>
       <c r="N17" s="26"/>
